--- a/artfynd/A 21068-2023 artfynd.xlsx
+++ b/artfynd/A 21068-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121559546</v>
+        <v>121559545</v>
       </c>
       <c r="B2" t="n">
-        <v>79689</v>
+        <v>98021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691334</v>
+        <v>691386</v>
       </c>
       <c r="R2" t="n">
-        <v>7135283</v>
+        <v>7135387</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121559552</v>
+        <v>121559542</v>
       </c>
       <c r="B3" t="n">
-        <v>97058</v>
+        <v>98125</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691279</v>
+        <v>691326</v>
       </c>
       <c r="R3" t="n">
-        <v>7135463</v>
+        <v>7135452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121559545</v>
+        <v>121559546</v>
       </c>
       <c r="B4" t="n">
-        <v>98021</v>
+        <v>79689</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691386</v>
+        <v>691334</v>
       </c>
       <c r="R4" t="n">
-        <v>7135387</v>
+        <v>7135283</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121559542</v>
+        <v>121559552</v>
       </c>
       <c r="B5" t="n">
-        <v>98125</v>
+        <v>97058</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691326</v>
+        <v>691279</v>
       </c>
       <c r="R5" t="n">
-        <v>7135452</v>
+        <v>7135463</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21068-2023 artfynd.xlsx
+++ b/artfynd/A 21068-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121559545</v>
+        <v>121559546</v>
       </c>
       <c r="B2" t="n">
-        <v>98021</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691386</v>
+        <v>691334</v>
       </c>
       <c r="R2" t="n">
-        <v>7135387</v>
+        <v>7135283</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121559542</v>
+        <v>121559545</v>
       </c>
       <c r="B3" t="n">
-        <v>98125</v>
+        <v>98022</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691326</v>
+        <v>691386</v>
       </c>
       <c r="R3" t="n">
-        <v>7135452</v>
+        <v>7135387</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121559546</v>
+        <v>121559542</v>
       </c>
       <c r="B4" t="n">
-        <v>79689</v>
+        <v>98126</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691334</v>
+        <v>691326</v>
       </c>
       <c r="R4" t="n">
-        <v>7135283</v>
+        <v>7135452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>121559552</v>
       </c>
       <c r="B5" t="n">
-        <v>97058</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 21068-2023 artfynd.xlsx
+++ b/artfynd/A 21068-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121559546</v>
+        <v>121559552</v>
       </c>
       <c r="B2" t="n">
-        <v>79690</v>
+        <v>97059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691334</v>
+        <v>691279</v>
       </c>
       <c r="R2" t="n">
-        <v>7135283</v>
+        <v>7135463</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121559545</v>
+        <v>121559546</v>
       </c>
       <c r="B3" t="n">
-        <v>98022</v>
+        <v>79690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691386</v>
+        <v>691334</v>
       </c>
       <c r="R3" t="n">
-        <v>7135387</v>
+        <v>7135283</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121559552</v>
+        <v>121559545</v>
       </c>
       <c r="B5" t="n">
-        <v>97059</v>
+        <v>98022</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691279</v>
+        <v>691386</v>
       </c>
       <c r="R5" t="n">
-        <v>7135463</v>
+        <v>7135387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21068-2023 artfynd.xlsx
+++ b/artfynd/A 21068-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121559552</v>
+        <v>121559546</v>
       </c>
       <c r="B2" t="n">
-        <v>97059</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691279</v>
+        <v>691334</v>
       </c>
       <c r="R2" t="n">
-        <v>7135463</v>
+        <v>7135283</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121559546</v>
+        <v>121559542</v>
       </c>
       <c r="B3" t="n">
-        <v>79690</v>
+        <v>98126</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691334</v>
+        <v>691326</v>
       </c>
       <c r="R3" t="n">
-        <v>7135283</v>
+        <v>7135452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121559542</v>
+        <v>121559552</v>
       </c>
       <c r="B4" t="n">
-        <v>98126</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691326</v>
+        <v>691279</v>
       </c>
       <c r="R4" t="n">
-        <v>7135452</v>
+        <v>7135463</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 21068-2023 artfynd.xlsx
+++ b/artfynd/A 21068-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121559542</v>
+        <v>121559552</v>
       </c>
       <c r="B3" t="n">
-        <v>98126</v>
+        <v>97059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691326</v>
+        <v>691279</v>
       </c>
       <c r="R3" t="n">
-        <v>7135452</v>
+        <v>7135463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121559552</v>
+        <v>121559542</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
+        <v>98126</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691279</v>
+        <v>691326</v>
       </c>
       <c r="R4" t="n">
-        <v>7135463</v>
+        <v>7135452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 21068-2023 artfynd.xlsx
+++ b/artfynd/A 21068-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121559546</v>
       </c>
       <c r="B2" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121559552</v>
+        <v>121559545</v>
       </c>
       <c r="B3" t="n">
-        <v>97059</v>
+        <v>98030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691279</v>
+        <v>691386</v>
       </c>
       <c r="R3" t="n">
-        <v>7135463</v>
+        <v>7135387</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121559542</v>
+        <v>121559552</v>
       </c>
       <c r="B4" t="n">
-        <v>98126</v>
+        <v>97067</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691326</v>
+        <v>691279</v>
       </c>
       <c r="R4" t="n">
-        <v>7135452</v>
+        <v>7135463</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121559545</v>
+        <v>121559542</v>
       </c>
       <c r="B5" t="n">
-        <v>98022</v>
+        <v>98134</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691386</v>
+        <v>691326</v>
       </c>
       <c r="R5" t="n">
-        <v>7135387</v>
+        <v>7135452</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21068-2023 artfynd.xlsx
+++ b/artfynd/A 21068-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121559545</v>
+        <v>121559546</v>
       </c>
       <c r="B2" t="n">
-        <v>98030</v>
+        <v>79697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691386</v>
+        <v>691334</v>
       </c>
       <c r="R2" t="n">
-        <v>7135387</v>
+        <v>7135283</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121559542</v>
+        <v>121559552</v>
       </c>
       <c r="B3" t="n">
-        <v>98134</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691326</v>
+        <v>691279</v>
       </c>
       <c r="R3" t="n">
-        <v>7135452</v>
+        <v>7135463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121559552</v>
+        <v>121559542</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>98134</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691279</v>
+        <v>691326</v>
       </c>
       <c r="R4" t="n">
-        <v>7135463</v>
+        <v>7135452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121559546</v>
+        <v>121559545</v>
       </c>
       <c r="B5" t="n">
-        <v>79697</v>
+        <v>98030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691334</v>
+        <v>691386</v>
       </c>
       <c r="R5" t="n">
-        <v>7135283</v>
+        <v>7135387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21068-2023 artfynd.xlsx
+++ b/artfynd/A 21068-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121559546</v>
+        <v>121559542</v>
       </c>
       <c r="B2" t="n">
-        <v>79697</v>
+        <v>98134</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691334</v>
+        <v>691326</v>
       </c>
       <c r="R2" t="n">
-        <v>7135283</v>
+        <v>7135452</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121559542</v>
+        <v>121559546</v>
       </c>
       <c r="B4" t="n">
-        <v>98134</v>
+        <v>79697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691326</v>
+        <v>691334</v>
       </c>
       <c r="R4" t="n">
-        <v>7135452</v>
+        <v>7135283</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
